--- a/data/trans_dic/P25C$smedicoempresa_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,91</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,7</t>
+          <t>0,05; 0,67</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3302</t>
+          <t>0; 3402</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>0; 2306</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3570</t>
+          <t>0; 3660</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6939</t>
+          <t>0; 5767</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1221</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7057</t>
+          <t>0; 5641</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5250</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1156</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4359</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1453</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1262</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1396</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2741</t>
+          <t>0; 2761</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1190</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2869</t>
+          <t>0; 2649</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1843</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1169</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1264</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>433; 7624</t>
+          <t>0; 7570</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1946</t>
+          <t>0; 2304</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>474; 8184</t>
+          <t>632; 7794</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$smedicoempresa_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -782,14 +782,14 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,09; 0,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,67</t>
+          <t>0,06; 0,72</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>624</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3402</t>
+          <t>0; 3815</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2306</t>
+          <t>0; 2198</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3660</t>
+          <t>0; 3529</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1084</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5767</t>
+          <t>0; 7085</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5641</t>
+          <t>0; 5562</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2761</t>
+          <t>0; 2758</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1334,14 +1334,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2649</t>
+          <t>0; 2880</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 7570</t>
+          <t>560; 6186</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2304</t>
+          <t>0; 2163</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>632; 7794</t>
+          <t>640; 7216</t>
         </is>
       </c>
     </row>
